--- a/downloads/drjohnson.xlsx
+++ b/downloads/drjohnson.xlsx
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Johnson elsewhere online</t>
+          <t>Dr. Johnson in the press, podcasts and directories</t>
         </is>
       </c>
     </row>

--- a/downloads/drjohnson.xlsx
+++ b/downloads/drjohnson.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professional records and regist" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspaper and magazine coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="His columns in Danville Today," sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registries and records" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Press coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="His newspaper columns" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Podcasts and videos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professional events and talks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saved copies of the cited pages" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events and talks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saved copies" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Professional records and regist</t>
+          <t>Registries and records</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -495,7 +495,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Newspaper and magazine coverage</t>
+          <t>Press coverage</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -510,7 +510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>His columns in Danville Today,</t>
+          <t>His newspaper columns</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -540,7 +540,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Professional events and talks</t>
+          <t>Events and talks</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -555,7 +555,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Saved copies of the cited pages</t>
+          <t>Saved copies</t>
         </is>
       </c>
       <c r="B10" t="n">

--- a/downloads/drjohnson.xlsx
+++ b/downloads/drjohnson.xlsx
@@ -593,7 +593,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,7 +703,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy 2003 · last copy 2006 · all dates</t>
+          <t>first copy 2003 · last copy 2006 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy 2010 · last copy 2023 · all dates</t>
+          <t>first copy 2010 · last copy 2023 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy 2023 · last copy 2023 · all dates</t>
+          <t>first copy 2023 · last copy 2023 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,7 +882,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy 2012 · last copy 2013 · all dates</t>
+          <t>first copy 2012 · last copy 2013 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>first copy 2012 · last copy 2013 · all dates</t>
+          <t>first copy 2012 · last copy 2013 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy 2024 · last copy 2024 · all dates</t>
+          <t>first copy 2024 · last copy 2024 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy 2021 · last copy 2025 · all dates</t>
+          <t>first copy 2021 · last copy 2025 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy 2017 · last copy 2017 · all dates</t>
+          <t>first copy 2017 · last copy 2017 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy 2018 · last copy 2025 · all dates</t>
+          <t>first copy 2018 · last copy 2025 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy 2010 · last copy 2016 · all dates</t>
+          <t>first copy 2010 · last copy 2016 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy 2013 · last copy 2026 · all dates</t>
+          <t>first copy 2013 · last copy 2026 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy 2021 · last copy 2026 · all dates</t>
+          <t>first copy 2021 · last copy 2026 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy 2007 · last copy 2008 · all dates</t>
+          <t>first copy 2007 · last copy 2008 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>first copy 2022 · last copy 2022 · all dates</t>
+          <t>first copy 2022 · last copy 2022 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy 2017 · last copy 2026 · all dates</t>
+          <t>first copy 2017 · last copy 2026 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy 2024 · last copy 2024 · all dates</t>
+          <t>first copy 2024 · last copy 2024 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy 2024 · last copy 2024 · all dates</t>
+          <t>first copy 2024 · last copy 2024 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>first copy 2009 · last copy 2021 · all dates</t>
+          <t>first copy 2009 · last copy 2021 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy 2004 · last copy 2021 · all dates</t>
+          <t>first copy 2004 · last copy 2021 · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>first copy 2012 · last copy 2019 · all dates</t>
+          <t>first copy 2012 · last copy 2019 · latest saved copy</t>
         </is>
       </c>
     </row>
